--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDisplayName.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDisplayName.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,6 +968,30 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>전기 속성 보너스</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stat.normaldamagepercent</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>일반공격 피해%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stat.skilldamagepercent</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>스킬 피해%</t>
         </is>
       </c>
     </row>
@@ -982,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,6 +1558,30 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>Electric Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stat.normaldamagepercent</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Normal Attack Damage%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stat.skilldamagepercent</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Skill Damage%</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2100,6 +2148,30 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>電気属性ボーナス</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stat.normaldamagepercent</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>通常攻撃ダメージ%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stat.skilldamagepercent</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>スキルダメージ%</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,6 +2741,30 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>stat.normaldamagepercent</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>普通攻击伤害%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>stat.skilldamagepercent</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>技能伤害%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDisplayName.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/ItemDisplayName.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>체력%</t>
+          <t>체력</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공격력%</t>
+          <t>공격력</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>방어력%</t>
+          <t>방어력</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>이동속도%</t>
+          <t>이동속도</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공격속도%</t>
+          <t>공격속도</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MP 재생력%</t>
+          <t>MP 재생력</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>스킬 범위%</t>
+          <t>스킬 범위</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>일반공격 피해%</t>
+          <t>일반공격 피해</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>스킬 피해%</t>
+          <t>스킬 피해</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Health%</t>
+          <t>Health</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Attack%</t>
+          <t>Attack</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Defense%</t>
+          <t>Defense</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Move Speed%</t>
+          <t>Move Speed</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Attack Speed%</t>
+          <t>Attack Speed</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MP Regen%</t>
+          <t>MP Regen</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Skill Range%</t>
+          <t>Skill Range</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Normal Attack Damage%</t>
+          <t>Normal Attack Damage</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Skill Damage%</t>
+          <t>Skill Damage</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>体力%</t>
+          <t>体力</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>攻撃力%</t>
+          <t>攻撃力</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>防御力%</t>
+          <t>防御力</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>移動速度%</t>
+          <t>移動速度</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>攻撃速度%</t>
+          <t>攻撃速度</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MP再生力%</t>
+          <t>MP再生力</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>スキル範囲%</t>
+          <t>スキル範囲</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>通常攻撃ダメージ%</t>
+          <t>通常攻撃ダメージ</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>スキルダメージ%</t>
+          <t>スキルダメージ</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>体力%</t>
+          <t>体力</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>攻击力%</t>
+          <t>攻击力</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>防御力%</t>
+          <t>防御力</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>移动速度%</t>
+          <t>移动速度</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>攻击速度%</t>
+          <t>攻击速度</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MP回复%</t>
+          <t>MP回复</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>技能范围%</t>
+          <t>技能范围</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>普通攻击伤害%</t>
+          <t>普通攻击伤害</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>技能伤害%</t>
+          <t>技能伤害</t>
         </is>
       </c>
     </row>
